--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260804.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260804.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>151,885</t>
+          <t>151,535</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>28.46%</t>
+          <t>29.35%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>17,315</t>
+          <t>17,215</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>8.12%</t>
         </is>
       </c>
     </row>
@@ -655,56 +655,56 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>110,050</t>
+          <t>109,950</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.46%</t>
+          <t>7.42%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>NEE US</t>
+          <t>MRVL US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Marvell Technology Inc</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>133,945</t>
+          <t>55,925</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.54%</t>
+          <t>5.66%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MRVL US</t>
+          <t>NEE US</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Marvell Technology Inc</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>56,025</t>
+          <t>133,645</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.19%</t>
+          <t>5.40%</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>65,770</t>
+          <t>65,620</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>72,405</t>
+          <t>72,205</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>6,325</t>
+          <t>6,225</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -787,56 +787,56 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>50,035</t>
+          <t>49,885</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>21,825</t>
+          <t>20,133</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>20,233</t>
+          <t>21,725</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
@@ -853,56 +853,56 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>34,860</t>
+          <t>34,760</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>22,445</t>
+          <t>84,705</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>84,905</t>
+          <t>22,345</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -919,34 +919,34 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>56,495</t>
+          <t>56,295</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>21,570</t>
+          <t>8,790</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>29,348</t>
+          <t>29,248</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -985,56 +985,56 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>40,070</t>
+          <t>39,920</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>65,698</t>
+          <t>21,470</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>8,790</t>
+          <t>65,498</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
@@ -1073,56 +1073,56 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>23,568</t>
+          <t>23,468</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>140,445</t>
+          <t>10,566</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>10,566</t>
+          <t>139,845</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
@@ -1139,34 +1139,34 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>20,405</t>
+          <t>20,305</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>17,571</t>
+          <t>2,052,927</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1188,117 +1188,117 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>59,711,247</t>
+          <t>17,471</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>13,005</t>
+          <t>41,500</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>41,650</t>
+          <t>47,690</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>47,840</t>
+          <t>54,827,557</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>984,134</t>
+          <t>13,005</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>48,705,000</t>
+          <t>64,940,500</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,068,793</t>
+          <t>685,982</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
